--- a/staff_forms/014_skill_set_evaluation_form--staff_forms.xlsx
+++ b/staff_forms/014_skill_set_evaluation_form--staff_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -958,17 +958,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>programming_languages_choices</t>
+          <t>development_environment_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>c#</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>windows</t>
+          <t>linux</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Windows</t>
+          <t>Linux</t>
         </is>
       </c>
     </row>
@@ -997,29 +997,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>linux</t>
+          <t>mac</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Mac</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>development_environment_choices</t>
+          <t>databases_used_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mac</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mac</t>
+          <t>SQL</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>nosql</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>NoSQL</t>
         </is>
       </c>
     </row>
@@ -1048,29 +1048,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nosql</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NoSQL</t>
+          <t>Oracle</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>databases_used_choices</t>
+          <t>programming_languages_proficient_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>c++</t>
+          <t>c#</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>C#</t>
         </is>
       </c>
     </row>
@@ -1099,29 +1099,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>c#</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>programming_languages_proficient_choices</t>
+          <t>evaluation_score_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1184,27 +1184,10 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>evaluation_score_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
